--- a/테크로스_PLC_견적서.xlsx
+++ b/테크로스_PLC_견적서.xlsx
@@ -42,6 +42,111 @@
     <r>
       <rPr>
         <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">동인엔시스</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">견적일자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">일</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">대표자</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <color rgb="FF0000FF"/>
         <rFont val="맑은 고딕"/>
         <family val="0"/>
@@ -56,7 +161,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">회사명</t>
+      <t xml:space="preserve">대표자</t>
     </r>
     <r>
       <rPr>
@@ -66,73 +171,156 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">]      (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">수    신</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">테크로스 전략구매팀 귀하</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">사업자번호</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[   -  -     ]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">건    명</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">교체 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(TSU · ANU · ANU-S · MCC) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">견적</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">주소</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">주소</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">]</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">견적일자</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">년 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">월 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">일</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">대표자</t>
+    <t xml:space="preserve">유효기간</t>
   </si>
   <si>
     <r>
@@ -152,7 +340,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">대표자</t>
+      <t xml:space="preserve">견적일로부터    일</t>
     </r>
     <r>
       <rPr>
@@ -162,124 +350,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">]      (</t>
-    </r>
+      <t xml:space="preserve">]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">담당/연락처</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">인</t>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
         <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">수    신</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">주</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">테크로스 전략구매팀 귀하</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">사업자번호</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[   -  -     ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">건    명</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">교체 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(TSU · ANU · ANU-S · MCC) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">주소</t>
-  </si>
-  <si>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">담당자</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -288,7 +384,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">[</t>
+      <t xml:space="preserve">] / [</t>
     </r>
     <r>
       <rPr>
@@ -297,7 +393,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">주소</t>
+      <t xml:space="preserve">연락처</t>
     </r>
     <r>
       <rPr>
@@ -311,297 +407,13 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">유효기간</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">견적일로부터    일</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">담당</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="8"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연락처</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">[</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">담당자</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">] / [</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연락처</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">아래와 같이 견적합니다</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">.  (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">단위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, VAT </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">별도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 예상 금액 — </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사양 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">권장</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 예상 금액 — </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AC220V </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">사양</t>
-    </r>
+    <t xml:space="preserve">아래와 같이 견적합니다.  (단위: 원, VAT 별도)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 예상 금액 — DC24V 사양 (권장)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 예상 금액 — AC220V 사양</t>
   </si>
   <si>
     <r>
@@ -1541,50 +1353,10 @@
     <t xml:space="preserve">연간 수량</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 금액 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DC24V</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">연간 금액 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AC220V</t>
-    </r>
+    <t xml:space="preserve">연간 금액 DC24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">연간 금액 AC220V</t>
   </si>
   <si>
     <r>
@@ -2065,6 +1837,7 @@
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2072,6 +1845,7 @@
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2086,12 +1860,7 @@
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2107,24 +1876,16 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
-      <charset val="1"/>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2133,13 +1894,6 @@
       <color rgb="FF000000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2175,6 +1929,28 @@
     </font>
     <font>
       <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="0"/>
@@ -2275,8 +2051,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2296,15 +2076,35 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2312,51 +2112,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2364,7 +2144,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2372,19 +2152,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2647,1024 +2427,1024 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="3"/>
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="3"/>
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="6"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="3"/>
+      <c r="C7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="4"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="8" t="str">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="9" t="str">
         <f aca="false">"₩ "&amp;TEXT(G48,"#,##0")</f>
         <v>₩ 441,900,000</v>
       </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8" t="str">
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="9" t="str">
         <f aca="false">"₩ "&amp;TEXT(H48,"#,##0")</f>
         <v>₩ 441,900,000</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="F15" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="17" t="n">
         <v>494000</v>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="17" t="n">
         <f aca="false">F15*G15</f>
         <v>494000</v>
       </c>
-      <c r="I15" s="17"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="19" t="n">
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="20" t="n">
         <f aca="false">SUM(H15:H15)</f>
         <v>494000</v>
       </c>
-      <c r="I16" s="20"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="F17" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="17" t="n">
         <v>646000</v>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="17" t="n">
         <f aca="false">F17*G17</f>
         <v>646000</v>
       </c>
-      <c r="I17" s="17"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="19" t="n">
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="20" t="n">
         <f aca="false">SUM(H17:H17)</f>
         <v>646000</v>
       </c>
-      <c r="I18" s="20"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="17" t="n">
         <v>494000</v>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="17" t="n">
         <f aca="false">F19*G19</f>
         <v>494000</v>
       </c>
-      <c r="I19" s="17"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="14"/>
+      <c r="C20" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="17" t="n">
         <v>152000</v>
       </c>
-      <c r="H20" s="16" t="n">
+      <c r="H20" s="17" t="n">
         <f aca="false">F20*G20</f>
         <v>152000</v>
       </c>
-      <c r="I20" s="17"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="19" t="n">
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="20" t="n">
         <f aca="false">SUM(H19:H20)</f>
         <v>646000</v>
       </c>
-      <c r="I21" s="20"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="17" t="n">
         <v>350800</v>
       </c>
-      <c r="H22" s="16" t="n">
+      <c r="H22" s="17" t="n">
         <f aca="false">F22*G22</f>
         <v>350800</v>
       </c>
-      <c r="I22" s="17"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="14" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="17" t="n">
         <v>76100</v>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="17" t="n">
         <f aca="false">F23*G23</f>
         <v>380500</v>
       </c>
-      <c r="I23" s="17"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="14" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="17" t="n">
         <v>75800</v>
       </c>
-      <c r="H24" s="16" t="n">
+      <c r="H24" s="17" t="n">
         <f aca="false">F24*G24</f>
         <v>151600</v>
       </c>
-      <c r="I24" s="17"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="14" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="F25" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="17" t="n">
         <v>56100</v>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="17" t="n">
         <f aca="false">F25*G25</f>
         <v>56100</v>
       </c>
-      <c r="I25" s="17"/>
+      <c r="I25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="14" t="s">
+      <c r="B26" s="14"/>
+      <c r="C26" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G26" s="16" t="n">
+      <c r="G26" s="17" t="n">
         <v>117200</v>
       </c>
-      <c r="H26" s="16" t="n">
+      <c r="H26" s="17" t="n">
         <f aca="false">F26*G26</f>
         <v>117200</v>
       </c>
-      <c r="I26" s="17"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="14" t="s">
+      <c r="B27" s="14"/>
+      <c r="C27" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="17" t="n">
         <v>52100</v>
       </c>
-      <c r="H27" s="16" t="n">
+      <c r="H27" s="17" t="n">
         <f aca="false">F27*G27</f>
         <v>52100</v>
       </c>
-      <c r="I27" s="17"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="14" t="s">
+      <c r="B28" s="14"/>
+      <c r="C28" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="16" t="n">
+      <c r="G28" s="17" t="n">
         <v>61700</v>
       </c>
-      <c r="H28" s="16" t="n">
+      <c r="H28" s="17" t="n">
         <f aca="false">F28*G28</f>
         <v>61700</v>
       </c>
-      <c r="I28" s="17"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="19" t="n">
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20" t="n">
         <f aca="false">SUM(H22:H28)</f>
         <v>1170000</v>
       </c>
-      <c r="I29" s="20"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="H32" s="11" t="s">
+      <c r="H32" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="17" t="n">
         <v>494000</v>
       </c>
-      <c r="H33" s="16" t="n">
+      <c r="H33" s="17" t="n">
         <f aca="false">F33*G33</f>
         <v>494000</v>
       </c>
-      <c r="I33" s="17"/>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="19" t="n">
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="20" t="n">
         <f aca="false">SUM(H33:H33)</f>
         <v>494000</v>
       </c>
-      <c r="I34" s="20"/>
+      <c r="I34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="17" t="n">
         <v>646000</v>
       </c>
-      <c r="H35" s="16" t="n">
+      <c r="H35" s="17" t="n">
         <f aca="false">F35*G35</f>
         <v>646000</v>
       </c>
-      <c r="I35" s="17"/>
+      <c r="I35" s="18"/>
     </row>
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="19" t="n">
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="20" t="n">
         <f aca="false">SUM(H35:H35)</f>
         <v>646000</v>
       </c>
-      <c r="I36" s="20"/>
+      <c r="I36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="C37" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G37" s="16" t="n">
+      <c r="G37" s="17" t="n">
         <v>494000</v>
       </c>
-      <c r="H37" s="16" t="n">
+      <c r="H37" s="17" t="n">
         <f aca="false">F37*G37</f>
         <v>494000</v>
       </c>
-      <c r="I37" s="17"/>
+      <c r="I37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="n">
+      <c r="A38" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="14" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="12" t="s">
+      <c r="E38" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="16" t="n">
+      <c r="G38" s="17" t="n">
         <v>152000</v>
       </c>
-      <c r="H38" s="16" t="n">
+      <c r="H38" s="17" t="n">
         <f aca="false">F38*G38</f>
         <v>152000</v>
       </c>
-      <c r="I38" s="17"/>
+      <c r="I38" s="18"/>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="19" t="n">
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="20" t="n">
         <f aca="false">SUM(H37:H38)</f>
         <v>646000</v>
       </c>
-      <c r="I39" s="20"/>
+      <c r="I39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="21"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="21"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="22"/>
+      <c r="I40" s="22"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="10" t="s">
+      <c r="B43" s="12"/>
+      <c r="C43" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="11" t="s">
+      <c r="E43" s="11"/>
+      <c r="F43" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="G43" s="11" t="s">
+      <c r="G43" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I43" s="11"/>
+      <c r="I43" s="12"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="14"/>
+      <c r="C44" s="17" t="n">
         <f aca="false">H16</f>
         <v>494000</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <f aca="false">H34</f>
         <v>494000</v>
       </c>
-      <c r="E44" s="16"/>
-      <c r="F44" s="22" t="n">
+      <c r="E44" s="17"/>
+      <c r="F44" s="23" t="n">
         <v>200</v>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="17" t="n">
         <f aca="false">C44*F44</f>
         <v>98800000</v>
       </c>
-      <c r="H44" s="16" t="n">
+      <c r="H44" s="17" t="n">
         <f aca="false">D44*F44</f>
         <v>98800000</v>
       </c>
-      <c r="I44" s="23"/>
+      <c r="I44" s="24"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="16" t="n">
+      <c r="B45" s="14"/>
+      <c r="C45" s="17" t="n">
         <f aca="false">H18</f>
         <v>646000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <f aca="false">H36</f>
         <v>646000</v>
       </c>
-      <c r="E45" s="16"/>
-      <c r="F45" s="22" t="n">
+      <c r="E45" s="17"/>
+      <c r="F45" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="17" t="n">
         <f aca="false">C45*F45</f>
         <v>193800000</v>
       </c>
-      <c r="H45" s="16" t="n">
+      <c r="H45" s="17" t="n">
         <f aca="false">D45*F45</f>
         <v>193800000</v>
       </c>
-      <c r="I45" s="23"/>
+      <c r="I45" s="24"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="16" t="n">
+      <c r="B46" s="14"/>
+      <c r="C46" s="17" t="n">
         <f aca="false">H21</f>
         <v>646000</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <f aca="false">H39</f>
         <v>646000</v>
       </c>
-      <c r="E46" s="16"/>
-      <c r="F46" s="22" t="n">
+      <c r="E46" s="17"/>
+      <c r="F46" s="23" t="n">
         <v>50</v>
       </c>
-      <c r="G46" s="16" t="n">
+      <c r="G46" s="17" t="n">
         <f aca="false">C46*F46</f>
         <v>32300000</v>
       </c>
-      <c r="H46" s="16" t="n">
+      <c r="H46" s="17" t="n">
         <f aca="false">D46*F46</f>
         <v>32300000</v>
       </c>
-      <c r="I46" s="23"/>
+      <c r="I46" s="24"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="16" t="n">
+      <c r="B47" s="14"/>
+      <c r="C47" s="17" t="n">
         <f aca="false">H29</f>
         <v>1170000</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="17" t="n">
         <f aca="false">H29</f>
         <v>1170000</v>
       </c>
-      <c r="E47" s="16"/>
-      <c r="F47" s="22" t="n">
+      <c r="E47" s="17"/>
+      <c r="F47" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G47" s="17" t="n">
         <f aca="false">C47*F47</f>
         <v>117000000</v>
       </c>
-      <c r="H47" s="16" t="n">
+      <c r="H47" s="17" t="n">
         <f aca="false">D47*F47</f>
         <v>117000000</v>
       </c>
-      <c r="I47" s="23" t="s">
+      <c r="I47" s="24" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+      <c r="A48" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="24" t="n">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="25" t="n">
         <f aca="false">SUM(G44:G47)</f>
         <v>441900000</v>
       </c>
-      <c r="H48" s="24" t="n">
+      <c r="H48" s="25" t="n">
         <f aca="false">SUM(H44:H47)</f>
         <v>441900000</v>
       </c>
-      <c r="I48" s="25"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="26" t="s">
+      <c r="I48" s="26"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="27" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="27" t="s">
+      <c r="A51" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
     </row>
     <row r="52" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
     </row>
     <row r="53" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="27" t="s">
+      <c r="A53" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="28"/>
+      <c r="F53" s="28"/>
+      <c r="G53" s="28"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="28"/>
     </row>
     <row r="54" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="27" t="s">
+      <c r="A54" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
     </row>
     <row r="55" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="52">
